--- a/data/trans_orig/Q70-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q70-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,96</t>
+          <t>8,47</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,56</t>
+          <t>8,8</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,79</t>
+          <t>8,61</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,53</t>
+          <t>0,15; 0,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,51</t>
+          <t>0,39; 2,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,89</t>
+          <t>0,82; 4,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 17,55</t>
+          <t>5,36; 14,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,91</t>
+          <t>0,28; 1,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,32</t>
+          <t>0,42; 2,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 22,14</t>
+          <t>3,31; 23,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 15,21</t>
+          <t>5,39; 13,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,61</t>
+          <t>0,24; 0,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,99</t>
+          <t>0,51; 2,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,39</t>
+          <t>2,4; 10,03</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 13,89</t>
+          <t>6,18; 12,4</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,38</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,03</t>
+          <t>5,7</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>4,92</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,39</t>
+          <t>1,13; 5,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,63</t>
+          <t>0,27; 1,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,77</t>
+          <t>0,99; 3,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 13,56</t>
+          <t>1,88; 13,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,07</t>
+          <t>2,07; 10,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,85</t>
+          <t>0,09; 0,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,8</t>
+          <t>0,51; 5,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 11,99</t>
+          <t>2,81; 11,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,36</t>
+          <t>1,7; 5,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,16</t>
+          <t>0,24; 1,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,41</t>
+          <t>0,97; 3,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 11,65</t>
+          <t>2,93; 10,15</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>8,49</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,32</t>
+          <t>14,29</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,12</t>
+          <t>11,1</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,49</t>
+          <t>0,32; 3,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,99</t>
+          <t>0,69; 4,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 8,8</t>
+          <t>0,52; 8,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 17,13</t>
+          <t>4,24; 16,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,08</t>
+          <t>0,21; 2,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,86</t>
+          <t>0,63; 2,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,58</t>
+          <t>0,03; 0,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 23,54</t>
+          <t>8,43; 24,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,02</t>
+          <t>0,38; 1,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,37</t>
+          <t>0,85; 3,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,02</t>
+          <t>0,33; 4,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 16,98</t>
+          <t>7,23; 16,89</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,82</t>
+          <t>13,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>8,6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,95</t>
+          <t>11,05</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,43</t>
+          <t>0,49; 2,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,34</t>
+          <t>0,22; 1,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 18,8</t>
+          <t>1,18; 21,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 31,03</t>
+          <t>6,6; 28,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,02</t>
+          <t>0,3; 1,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 10,7</t>
+          <t>0,2; 9,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 8,45</t>
+          <t>0,69; 8,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 10,63</t>
+          <t>4,52; 17,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,8</t>
+          <t>0,48; 1,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,22</t>
+          <t>0,34; 4,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 12,6</t>
+          <t>1,64; 12,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 14,43</t>
+          <t>6,77; 19,35</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,09</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>3,65</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,53</t>
+          <t>0,62; 2,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,03</t>
+          <t>0,42; 6,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,38</t>
+          <t>0,37; 1,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,05</t>
+          <t>2,15; 7,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,7</t>
+          <t>0,25; 3,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 45,99</t>
+          <t>5,32; 47,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,48</t>
+          <t>0,18; 1,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,73</t>
+          <t>2,1; 5,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,18</t>
+          <t>0,67; 2,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 18,02</t>
+          <t>2,87; 18,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,12</t>
+          <t>0,37; 1,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,76</t>
+          <t>2,46; 5,6</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>9,63</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,95</t>
+          <t>10,07</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,0</t>
+          <t>9,8</t>
         </is>
       </c>
     </row>
@@ -1421,57 +1421,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,75</t>
+          <t>0,37; 3,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 7,59</t>
+          <t>1,08; 7,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,49; 23,19</t>
+          <t>4,81; 22,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 31,6</t>
+          <t>0,5; 22,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,13</t>
+          <t>0,49; 2,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,16</t>
+          <t>0,75; 6,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,2; 19,48</t>
+          <t>4,84; 21,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 9,07</t>
+          <t>0,25; 8,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,09</t>
+          <t>0,54; 2,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,97</t>
+          <t>1,22; 4,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,35; 18,64</t>
+          <t>5,69; 17,5</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,78</t>
+          <t>11,52</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,36</t>
+          <t>8,53</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,72</t>
+          <t>0,47; 4,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 9,85</t>
+          <t>1,17; 8,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,75</t>
+          <t>0,65; 1,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,91</t>
+          <t>3,44; 10,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,12</t>
+          <t>0,75; 6,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,12</t>
+          <t>0,32; 3,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,32</t>
+          <t>0,77; 4,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,06; 18,26</t>
+          <t>8,44; 16,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,77</t>
+          <t>0,8; 3,57</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,62</t>
+          <t>1,02; 5,69</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,34</t>
+          <t>0,81; 2,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,0; 13,06</t>
+          <t>6,43; 11,5</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>2,89</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>5,08</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,78</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,78</t>
+          <t>1,39; 3,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,63</t>
+          <t>0,65; 4,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,8</t>
+          <t>0,87; 6,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,63</t>
+          <t>1,91; 4,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,96</t>
+          <t>0,86; 1,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,05</t>
+          <t>0,58; 2,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,52</t>
+          <t>0,37; 3,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,99</t>
+          <t>3,86; 7,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,8</t>
+          <t>1,33; 2,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,48</t>
+          <t>0,83; 3,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,83</t>
+          <t>0,77; 3,89</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,26</t>
+          <t>2,94; 4,87</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>6,33</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8,13</t>
+          <t>8,4</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>7,24</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,05</t>
+          <t>1,08; 2,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,74</t>
+          <t>1,12; 2,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,55</t>
+          <t>1,39; 3,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,79</t>
+          <t>5,07; 8,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,29</t>
+          <t>1,26; 3,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,77</t>
+          <t>1,14; 3,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,38</t>
+          <t>1,29; 3,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,95</t>
+          <t>7,1; 10,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,15</t>
+          <t>1,23; 2,19</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,59</t>
+          <t>1,24; 2,6</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,94</t>
+          <t>1,57; 2,9</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,34</t>
+          <t>6,26; 8,64</t>
         </is>
       </c>
     </row>
